--- a/cl_st3_ph3_eyamrog/df_section_paragraph2.xlsx
+++ b/cl_st3_ph3_eyamrog/df_section_paragraph2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19">
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>156</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22">
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>152</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24">
@@ -852,11 +852,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Literature Review, Methodology, Results, Discussion</t>
+          <t>Introduction, Literature Review, Methodology, Results, Discussion</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25">
@@ -870,11 +870,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Literature Review, Methodology, Results, Discussion</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>801</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26">
@@ -888,11 +888,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Results</t>
+          <t>Methodology</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>436</v>
+        <v>824</v>
       </c>
     </row>
     <row r="27">
@@ -906,11 +906,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Results, Discussion</t>
+          <t>Results</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>441</v>
       </c>
     </row>
     <row r="28">
@@ -919,16 +919,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Biological Sciences</t>
+          <t>Health Sciences</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Results, Discussion, Conclusion</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>28</v>
+        <v>219</v>
       </c>
     </row>
     <row r="29">
@@ -942,11 +942,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Acknowledgements</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>219</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30">
@@ -960,11 +960,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Acknowledgements</t>
+          <t>Conclusion</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31">
@@ -978,11 +978,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Conclusion</t>
+          <t>Discussion</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>56</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -996,11 +996,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Discussion</t>
+          <t>Discussion, Conclusion</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>474</v>
       </c>
     </row>
     <row r="33">
@@ -1014,11 +1014,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Discussion, Conclusion</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>474</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34">
@@ -1032,11 +1032,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>Introduction, Literature Review</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>163</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35">
@@ -1050,11 +1050,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Introduction, Literature Review</t>
+          <t>Introduction, Literature Review, Methodology, Results, Discussion</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>225</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
@@ -1068,11 +1068,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Introduction, Literature Review, Methodology, Results, Discussion</t>
+          <t>Introduction, Literature Review, Results, Discussion, Conclusion</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Introduction, Literature Review, Results, Discussion, Conclusion</t>
+          <t>Literature Review</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -1104,11 +1104,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Literature Review</t>
+          <t>Literature Review, Methodology, Results</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
@@ -1122,11 +1122,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Literature Review, Methodology, Results</t>
+          <t>Literature Review, Methodology, Results, Discussion</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>30</v>
+        <v>564</v>
       </c>
     </row>
     <row r="40">
@@ -1140,11 +1140,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Literature Review, Methodology, Results, Discussion</t>
+          <t>Methodology</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>564</v>
+        <v>925</v>
       </c>
     </row>
     <row r="41">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Results</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>925</v>
+        <v>667</v>
       </c>
     </row>
     <row r="42">
@@ -1176,11 +1176,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Results</t>
+          <t>Results, Discussion</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>667</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43">
@@ -1189,16 +1189,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Health Sciences</t>
+          <t>Human Sciences</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Results, Discussion</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44">
@@ -1212,11 +1212,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Acknowledgements</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45">
@@ -1230,11 +1230,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Acknowledgements</t>
+          <t>Conclusion</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>42</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Conclusion</t>
+          <t>Discussion</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>79</v>
+        <v>236</v>
       </c>
     </row>
     <row r="47">
@@ -1266,11 +1266,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Discussion</t>
+          <t>Discussion, Conclusion</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>236</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48">
@@ -1284,11 +1284,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Discussion, Conclusion</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>53</v>
+        <v>154</v>
       </c>
     </row>
     <row r="49">
@@ -1302,11 +1302,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>Introduction, Literature Review</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>154</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50">
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Introduction, Literature Review</t>
+          <t>Literature Review, Methodology, Results, Discussion</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>194</v>
+        <v>611</v>
       </c>
     </row>
     <row r="51">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Literature Review, Methodology, Results, Discussion</t>
+          <t>Methodology</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>611</v>
+        <v>227</v>
       </c>
     </row>
     <row r="52">
@@ -1356,11 +1356,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Methodology, Results</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>227</v>
+        <v>96</v>
       </c>
     </row>
     <row r="53">
@@ -1374,11 +1374,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Methodology, Results</t>
+          <t>Results</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>96</v>
+        <v>244</v>
       </c>
     </row>
     <row r="54">
@@ -1387,16 +1387,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Human Sciences</t>
+          <t>Linguistic, literature and arts</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Results</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>244</v>
+        <v>29</v>
       </c>
     </row>
     <row r="55">
@@ -1410,11 +1410,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Acknowledgements</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56">
@@ -1428,11 +1428,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Acknowledgements</t>
+          <t>Conclusion</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>21</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57">
@@ -1446,11 +1446,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Conclusion</t>
+          <t>Discussion</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>83</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58">
@@ -1464,11 +1464,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Discussion</t>
+          <t>Discussion, Conclusion</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59">
@@ -1482,11 +1482,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Discussion, Conclusion</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>66</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60">
@@ -1500,11 +1500,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>Introduction, Literature Review</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>108</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
@@ -1518,11 +1518,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Introduction, Literature Review</t>
+          <t>Literature Review</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>19</v>
+        <v>245</v>
       </c>
     </row>
     <row r="62">
@@ -1536,11 +1536,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Literature Review</t>
+          <t>Literature Review, Methodology, Results</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>245</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63">
@@ -1554,11 +1554,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Literature Review, Methodology, Results</t>
+          <t>Literature Review, Methodology, Results, Discussion</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>50</v>
+        <v>192</v>
       </c>
     </row>
     <row r="64">
@@ -1572,11 +1572,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Literature Review, Methodology, Results, Discussion</t>
+          <t>Methodology</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>192</v>
+        <v>226</v>
       </c>
     </row>
     <row r="65">
@@ -1590,11 +1590,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Methodology, Results, Discussion</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>226</v>
+        <v>147</v>
       </c>
     </row>
     <row r="66">
@@ -1608,11 +1608,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Methodology, Results, Discussion</t>
+          <t>Results</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>147</v>
+        <v>268</v>
       </c>
     </row>
     <row r="67">
@@ -1626,28 +1626,10 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Results</t>
+          <t>Results, Discussion</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="n">
-        <v>66</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Linguistic, literature and arts</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Results, Discussion</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
         <v>224</v>
       </c>
     </row>
